--- a/output/results_0505_deficit_run2.xlsx
+++ b/output/results_0505_deficit_run2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dulin/Dropbox/UTHealth/SAFElab/LLM/UTH_IPSS_Pediatric Stroke/IPSS-GPT/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE8ADC01-71A5-7C44-90B2-722C4411C4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964D7E97-D774-8845-9C9E-D136FE7F96AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34040" yWindow="-1800" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1001,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1019,7 +1019,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1424,7 +1423,7 @@
       <c r="A4" s="1">
         <v>40</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" t="s">
         <v>47</v>
       </c>
       <c r="C4" t="s">
@@ -1433,7 +1432,7 @@
       <c r="D4" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>101</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -1450,7 +1449,7 @@
       <c r="A5" s="1">
         <v>38</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="s">
@@ -1473,7 +1472,7 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1490,7 +1489,7 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1507,7 +1506,7 @@
       <c r="A8" s="1">
         <v>14</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
@@ -1533,7 +1532,7 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1550,7 +1549,7 @@
       <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
@@ -1573,7 +1572,7 @@
       <c r="A11" s="1">
         <v>13</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
@@ -1582,7 +1581,7 @@
       <c r="D11" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>102</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1602,7 +1601,7 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
@@ -1626,7 +1625,7 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="s">
@@ -1650,7 +1649,7 @@
       <c r="A14" s="1">
         <v>6</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1667,7 +1666,7 @@
       <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -1693,7 +1692,7 @@
       <c r="A16" s="1">
         <v>35</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" t="s">
         <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -1710,7 +1709,7 @@
       <c r="A17" s="1">
         <v>39</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -1727,7 +1726,7 @@
       <c r="A18" s="1">
         <v>50</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -1744,7 +1743,7 @@
       <c r="A19" s="1">
         <v>33</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1773,7 +1772,7 @@
       <c r="A20" s="1">
         <v>49</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" t="s">
         <v>56</v>
       </c>
       <c r="C20" t="s">
@@ -1796,7 +1795,7 @@
       <c r="A21" s="1">
         <v>41</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" t="s">
         <v>48</v>
       </c>
       <c r="C21" t="s">
@@ -1822,7 +1821,7 @@
       <c r="A22" s="1">
         <v>45</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" t="s">
         <v>52</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -1839,7 +1838,7 @@
       <c r="A23" s="1">
         <v>32</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
@@ -1862,7 +1861,7 @@
       <c r="A24" s="1">
         <v>28</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" t="s">
         <v>35</v>
       </c>
       <c r="C24" t="s">
@@ -1885,7 +1884,7 @@
       <c r="A25" s="1">
         <v>46</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" t="s">
         <v>53</v>
       </c>
       <c r="C25" t="s">
@@ -1908,16 +1907,16 @@
       <c r="A26" s="1">
         <v>42</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" t="s">
         <v>49</v>
       </c>
       <c r="C26" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>157</v>
       </c>
       <c r="G26" s="8" t="s">
@@ -1934,7 +1933,7 @@
       <c r="A27" s="1">
         <v>16</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
@@ -1957,7 +1956,7 @@
       <c r="A28" s="1">
         <v>22</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" t="s">
         <v>29</v>
       </c>
       <c r="C28" t="s">
@@ -2449,7 +2448,7 @@
       <c r="D49" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="11" t="s">
         <v>162</v>
       </c>
       <c r="G49" s="6" t="s">
@@ -2540,7 +2539,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C56" s="13"/>
+      <c r="C56" s="12"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I52">
